--- a/data/trans_camb/IP18A05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,14</t>
+          <t>-2,82; 1,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,47</t>
+          <t>-2,22; 3,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 19,89</t>
+          <t>-0,64; 21,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 4,84</t>
+          <t>-0,34; 5,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,97</t>
+          <t>-2,96; 0,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 0,0</t>
+          <t>-3,45; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,43</t>
+          <t>-0,6; 2,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,62</t>
+          <t>-1,51; 1,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 9,99</t>
+          <t>-0,93; 8,35</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,25; 946,55</t>
+          <t>-70,96; 885,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,4</t>
+          <t>0,58; 3,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,8</t>
+          <t>-0,76; 1,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,98</t>
+          <t>-0,46; 1,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 14,07</t>
+          <t>1,36; 14,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,44</t>
+          <t>-0,07; 1,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,14</t>
+          <t>0,22; 2,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,03</t>
+          <t>0,81; 10,43</t>
         </is>
       </c>
     </row>
@@ -1109,32 +1109,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,62</t>
+          <t>0,43; 4,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,99</t>
+          <t>0,44; 3,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,66</t>
+          <t>0,0; 16,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,73</t>
+          <t>-0,73; 1,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 7,25</t>
+          <t>1,17; 7,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 20,42</t>
+          <t>1,25; 26,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,3</t>
+          <t>0,92; 4,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 15,07</t>
+          <t>2,05; 15,83</t>
         </is>
       </c>
     </row>
@@ -1325,27 +1325,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,09</t>
+          <t>-2,57; 1,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,41</t>
+          <t>-2,85; 0,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 9,26</t>
+          <t>-1,73; 9,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 1,58</t>
+          <t>-1,54; 1,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,07</t>
+          <t>-1,17; 2,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,94</t>
+          <t>-1,5; 0,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 0,66</t>
+          <t>-1,52; 0,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,33</t>
+          <t>-1,41; 3,39</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-86,62; 266,84</t>
+          <t>-100,0; 217,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 240,02</t>
+          <t>-100,0; 244,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,02</t>
+          <t>-0,64; 1,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,48</t>
+          <t>-0,3; 1,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 6,35</t>
+          <t>0,21; 5,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,46</t>
+          <t>-0,23; 1,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 1,94</t>
+          <t>0,03; 1,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 9,37</t>
+          <t>1,1; 8,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,98</t>
+          <t>-0,21; 0,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,36</t>
+          <t>0,06; 1,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,87</t>
+          <t>1,29; 5,97</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,21; 378,1</t>
+          <t>-64,24; 345,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,36; 642,13</t>
+          <t>-48,2; 507,61</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 2083,33</t>
+          <t>-22,09; 1973,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 697,45</t>
+          <t>-43,28; 626,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 732,12</t>
+          <t>-20,18; 801,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,9; 3292,96</t>
+          <t>77,55; 2683,06</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,19; 297,86</t>
+          <t>-25,52; 256,65</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 386,27</t>
+          <t>-3,21; 337,73</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>141,78; 1424,17</t>
+          <t>138,86; 1518,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Habitat-trans_camb.xlsx
@@ -677,22 +677,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,16</t>
+          <t>-2,89; 1,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 3,34</t>
+          <t>-1,9; 3,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 21,78</t>
+          <t>-0,64; 20,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,24</t>
+          <t>-0,58; 5,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,0</t>
+          <t>-4,43; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,5</t>
+          <t>-0,95; 2,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,64</t>
+          <t>-1,65; 1,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 8,35</t>
+          <t>-0,83; 8,45</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,96; 885,66</t>
+          <t>-68,29; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,1</t>
+          <t>0,6; 3,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,78</t>
+          <t>-0,76; 1,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,99</t>
+          <t>-0,53; 2,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 14,58</t>
+          <t>1,46; 15,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,46</t>
+          <t>-0,05; 1,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,09</t>
+          <t>0,29; 2,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 10,43</t>
+          <t>0,85; 9,68</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1109,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,01</t>
+          <t>0,43; 3,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,76</t>
+          <t>0,44; 3,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,67</t>
+          <t>0,0; 15,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,26</t>
+          <t>0,98; 7,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 26,8</t>
+          <t>1,26; 22,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,38</t>
+          <t>0,96; 4,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 15,83</t>
+          <t>1,96; 16,04</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,07</t>
+          <t>-2,53; 1,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,42</t>
+          <t>-2,79; 0,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 9,11</t>
+          <t>-1,65; 8,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,61</t>
+          <t>-1,52; 1,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,0</t>
+          <t>-1,16; 2,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,0</t>
+          <t>-2,32; 0,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,78</t>
+          <t>-1,45; 0,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,74</t>
+          <t>-1,54; 0,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,39</t>
+          <t>-1,38; 2,87</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 217,39</t>
+          <t>-85,0; 398,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 244,76</t>
+          <t>-100,0; 280,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,02</t>
+          <t>-0,64; 1,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,43</t>
+          <t>-0,26; 1,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,21; 5,72</t>
+          <t>0,31; 5,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,42</t>
+          <t>-0,28; 1,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,03; 1,86</t>
+          <t>-0,1; 1,8</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,53</t>
+          <t>1,2; 8,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,97</t>
+          <t>-0,18; 0,96</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,37</t>
+          <t>0,07; 1,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,97</t>
+          <t>1,24; 5,61</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,24; 345,79</t>
+          <t>-70,37; 416,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,2; 507,61</t>
+          <t>-39,25; 664,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 1973,84</t>
+          <t>-27,18; 1789,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,28; 626,39</t>
+          <t>-42,58; 602,17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 801,19</t>
+          <t>-28,23; 698,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,55; 2683,06</t>
+          <t>92,77; 2998,07</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 256,65</t>
+          <t>-26,17; 291,77</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 337,73</t>
+          <t>2,41; 499,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>138,86; 1518,28</t>
+          <t>145,15; 1477,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A05-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP18A05-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,26</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,59</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,28</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>4,95</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>1,88</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,14</t>
+          <t>-0,29; 4,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 3,39</t>
+          <t>-2,97; 0,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 20,94</t>
+          <t>-4,43; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 5,16</t>
+          <t>-2,86; 1,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,96</t>
+          <t>-1,82; 3,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 0,0</t>
+          <t>-1,25; 18,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,49</t>
+          <t>-0,89; 2,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,71</t>
+          <t>-1,44; 1,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 8,45</t>
+          <t>-0,87; 9,32</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>285,27%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-35,31%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-50,68%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>24,24%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>484,6%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>285,27%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-35,31%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>428,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>217,07%</t>
+          <t>199,8%</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-68,29; —</t>
+          <t>-70,25; 946,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -840,34 +840,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,42</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,73</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,54</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,06</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,52</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,87</t>
+          <t>4,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>-0,76; 1,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,4</t>
+          <t>-0,5; 1,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,37; 14,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,72</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,22</t>
+          <t>0,59; 3,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 15,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,48</t>
+          <t>-0,21; 1,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,32</t>
+          <t>0,23; 2,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 9,68</t>
+          <t>1,27; 10,75</t>
         </is>
       </c>
     </row>
@@ -946,34 +946,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>87,38%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>160,68%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1686,51%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>87,38%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>160,68%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1590,29%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>264,38%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1949,65%</t>
+          <t>2051,27%</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,26</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,67</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,59</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,26</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,58</t>
+          <t>5,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>6,57</t>
         </is>
       </c>
     </row>
@@ -1109,32 +1109,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,63</t>
+          <t>-0,73; 1,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,82</t>
+          <t>0,96; 7,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,1</t>
+          <t>0,66; 21,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,39</t>
+          <t>0,43; 3,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 7,48</t>
+          <t>0,44; 3,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 22,93</t>
+          <t>0,0; 19,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,59</t>
+          <t>0,96; 4,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,96; 16,04</t>
+          <t>1,76; 16,65</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>901,8%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2124,54%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>901,8%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2097,91%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>365,34%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3332,98%</t>
+          <t>3513,91%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,77</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,82</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>-0,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,11</t>
+          <t>-1,53; 1,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,44</t>
+          <t>-1,16; 2,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 8,77</t>
+          <t>-2,33; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,57</t>
+          <t>-2,47; 1,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,03</t>
+          <t>-2,89; 0,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,0</t>
+          <t>-1,93; 8,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,89</t>
+          <t>-1,48; 0,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,81</t>
+          <t>-1,59; 0,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,87</t>
+          <t>-1,35; 3,08</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15,13%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-37,34%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-66,78%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>55,97%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>15,13%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-5,37%</t>
+          <t>-11,85%</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-85,0; 398,74</t>
+          <t>-86,62; 266,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 280,7</t>
+          <t>-100,0; 240,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,55</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,86</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,96</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,23</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,54</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2,27</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,78</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,12</t>
+          <t>3,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,03</t>
+          <t>-0,18; 1,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,51</t>
+          <t>-0,04; 1,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 5,92</t>
+          <t>1,42; 10,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 1,4</t>
+          <t>-0,65; 1,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,8</t>
+          <t>-0,25; 1,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,48</t>
+          <t>0,29; 6,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,96</t>
+          <t>-0,24; 0,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,4</t>
+          <t>0,08; 1,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,61</t>
+          <t>1,4; 6,15</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>97,26%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>151,78%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>701,86%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>36,36%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>86,94%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>365,61%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>97,26%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>151,78%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>669,03%</t>
+          <t>363,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>527,48%</t>
+          <t>542,17%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-70,37; 416,36</t>
+          <t>-32,26; 697,45</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,25; 664,98</t>
+          <t>-24,92; 732,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 1789,85</t>
+          <t>88,0; 3811,2</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-42,58; 602,17</t>
+          <t>-64,21; 378,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 698,18</t>
+          <t>-45,36; 642,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,77; 2998,07</t>
+          <t>-25,93; 2111,86</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-26,17; 291,77</t>
+          <t>-31,19; 297,86</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,41; 499,06</t>
+          <t>-1,76; 386,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>145,15; 1477,68</t>
+          <t>145,17; 1492,17</t>
         </is>
       </c>
     </row>
